--- a/docs/TestCases_TaoSanPham.xlsx
+++ b/docs/TestCases_TaoSanPham.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\automation-test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DATN-automation-test\DATN_DangThiCamTu_v2\DATN_DangThiCamTu\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734D66CB-763C-4586-8D41-B63DCD677D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5CFB61B-F628-45BE-9A21-53AAA4F79E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="284">
   <si>
     <t>Condition ID</t>
   </si>
@@ -651,9 +651,6 @@
   </si>
   <si>
     <t>file: sample.docx</t>
-  </si>
-  <si>
-    <t>BUG đang mở: UI hiện không chặn, cho phép tải file .docx và bị lỗi sau đó. Cần log bug.</t>
   </si>
   <si>
     <t>Chỉ cho phép tối đa 1 ảnh</t>
@@ -1433,7 +1430,7 @@
         <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>14</v>
@@ -1454,7 +1451,7 @@
         <v>19</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K3" s="2"/>
     </row>
@@ -1464,7 +1461,7 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>20</v>
@@ -1512,7 +1509,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>28</v>
@@ -1543,7 +1540,7 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>34</v>
@@ -1576,7 +1573,7 @@
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>34</v>
@@ -1609,7 +1606,7 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>34</v>
@@ -1642,7 +1639,7 @@
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>28</v>
@@ -1690,7 +1687,7 @@
         <v>57</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>28</v>
@@ -1721,7 +1718,7 @@
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>28</v>
@@ -1742,7 +1739,7 @@
         <v>65</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K13" s="2"/>
     </row>
@@ -1752,7 +1749,7 @@
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>28</v>
@@ -1773,7 +1770,7 @@
         <v>69</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K14" s="2"/>
     </row>
@@ -1783,7 +1780,7 @@
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>34</v>
@@ -1801,7 +1798,7 @@
         <v>71</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>72</v>
@@ -1814,7 +1811,7 @@
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>34</v>
@@ -1832,10 +1829,10 @@
         <v>74</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K16" s="2"/>
     </row>
@@ -1862,7 +1859,7 @@
         <v>77</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>28</v>
@@ -1893,7 +1890,7 @@
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>28</v>
@@ -1926,7 +1923,7 @@
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>28</v>
@@ -1947,7 +1944,7 @@
         <v>19</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K20" s="2"/>
     </row>
@@ -1974,7 +1971,7 @@
         <v>92</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>34</v>
@@ -2005,7 +2002,7 @@
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>34</v>
@@ -2036,7 +2033,7 @@
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>28</v>
@@ -2069,7 +2066,7 @@
         <v>109</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>34</v>
@@ -2100,7 +2097,7 @@
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>28</v>
@@ -2145,10 +2142,10 @@
         <v>121</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>28</v>
@@ -2163,13 +2160,13 @@
         <v>30</v>
       </c>
       <c r="H28" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="I28" s="2" t="s">
+      <c r="J28" s="2" t="s">
         <v>282</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>283</v>
       </c>
       <c r="K28" s="2"/>
     </row>
@@ -2179,7 +2176,7 @@
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>28</v>
@@ -2210,7 +2207,7 @@
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>28</v>
@@ -2241,7 +2238,7 @@
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>34</v>
@@ -2272,7 +2269,7 @@
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>28</v>
@@ -2320,7 +2317,7 @@
         <v>141</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>34</v>
@@ -2351,7 +2348,7 @@
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>34</v>
@@ -2382,7 +2379,7 @@
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>34</v>
@@ -2413,7 +2410,7 @@
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>34</v>
@@ -2461,7 +2458,7 @@
         <v>158</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>28</v>
@@ -2494,7 +2491,7 @@
         <v>164</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>28</v>
@@ -2527,7 +2524,7 @@
         <v>170</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>28</v>
@@ -2575,7 +2572,7 @@
         <v>177</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>28</v>
@@ -2623,7 +2620,7 @@
         <v>184</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>28</v>
@@ -2654,7 +2651,7 @@
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>28</v>
@@ -2685,7 +2682,7 @@
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>28</v>
@@ -2706,11 +2703,9 @@
         <v>195</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="K47" s="6" t="s">
-        <v>196</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="K47" s="2"/>
     </row>
     <row r="48" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
@@ -2718,7 +2713,7 @@
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>28</v>
@@ -2727,25 +2722,25 @@
         <v>87</v>
       </c>
       <c r="F48" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="G48" s="2" t="s">
+      <c r="H48" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="H48" s="2" t="s">
+      <c r="I48" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="I48" s="2" t="s">
-        <v>200</v>
-      </c>
       <c r="J48" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K48" s="2"/>
     </row>
     <row r="49" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B49" s="9"/>
       <c r="C49" s="9"/>
@@ -2760,13 +2755,13 @@
     </row>
     <row r="50" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>203</v>
-      </c>
       <c r="C50" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>28</v>
@@ -2775,31 +2770,31 @@
         <v>87</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H50" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="I50" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="I50" s="2" t="s">
-        <v>271</v>
-      </c>
       <c r="J50" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="K50" s="2" t="s">
         <v>273</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>28</v>
@@ -2808,25 +2803,25 @@
         <v>87</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>19</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K51" s="2"/>
     </row>
     <row r="52" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B52" s="9"/>
       <c r="C52" s="9"/>
@@ -2841,13 +2836,13 @@
     </row>
     <row r="53" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>28</v>
@@ -2856,29 +2851,29 @@
         <v>50</v>
       </c>
       <c r="F53" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="G53" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G53" s="2" t="s">
+      <c r="H53" s="2" t="s">
         <v>212</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>213</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>19</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K53" s="2"/>
     </row>
     <row r="54" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>28</v>
@@ -2887,25 +2882,25 @@
         <v>50</v>
       </c>
       <c r="F54" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H54" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>216</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>19</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K54" s="2"/>
     </row>
     <row r="55" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B55" s="9"/>
       <c r="C55" s="9"/>
@@ -2920,34 +2915,34 @@
     </row>
     <row r="56" spans="1:11" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B56" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D56" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>220</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>19</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K56" s="2"/>
     </row>

--- a/docs/TestCases_TaoSanPham.xlsx
+++ b/docs/TestCases_TaoSanPham.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DATN-automation-test\DATN_DangThiCamTu_v2\DATN_DangThiCamTu\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5CFB61B-F628-45BE-9A21-53AAA4F79E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C17C96D8-7DB6-4B31-B290-DCDD23903AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="279">
   <si>
     <t>Condition ID</t>
   </si>
@@ -143,9 +143,6 @@
     <t>Lưu thành công, hiển thị "Thao tác thành công", quay về màn Quản lý sản phẩm và sản phẩm xuất hiện trong danh sách.</t>
   </si>
   <si>
-    <t>Cần verify chính xác 149 ký tự bằng tool</t>
-  </si>
-  <si>
     <t>Tạo sản phẩm thành công với Tên sản phẩm = 150 ký tự (biên trên hợp lệ)</t>
   </si>
   <si>
@@ -159,9 +156,6 @@
     <t>Lưu thành công, hiển thị "Thao tác thành công".</t>
   </si>
   <si>
-    <t>Cần verify chính xác 150 ký tự</t>
-  </si>
-  <si>
     <t>Tạo sản phẩm thất bại với Tên sản phẩm = 151 ký tự (vượt biên)</t>
   </si>
   <si>
@@ -173,9 +167,6 @@
   </si>
   <si>
     <t>Hiển thị thông báo "Tên sản phẩm không được dài quá 150 ký tự" màu đỏ phía dưới ô. Không gọi API lưu.</t>
-  </si>
-  <si>
-    <t>Cần verify chính xác 151 ký tự</t>
   </si>
   <si>
     <t>Medium</t>
@@ -299,9 +290,6 @@
     <t>DB lưu = 12.5; cả màn Quản lý sản phẩm VÀ màn Chi tiết sản phẩm đều hiển thị '12.5'.</t>
   </si>
   <si>
-    <t>BUG đang mở: hiện DB lưu 12.5 nhưng UI Chi tiết hiển thị 12 (mất phần thập phân). Cần log bug.</t>
-  </si>
-  <si>
     <t>Low</t>
   </si>
   <si>
@@ -885,9 +873,6 @@
   </si>
   <si>
     <t>Hệ thống hiển thị 'e12.5'</t>
-  </si>
-  <si>
-    <t>BUG</t>
   </si>
   <si>
     <t>Dropdown hiển thị 4 lựa chọn: g, kg, ml, l</t>
@@ -926,7 +911,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -951,19 +936,13 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -988,11 +967,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFE699"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4B084"/>
       </patternFill>
     </fill>
     <fill>
@@ -1028,7 +1002,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1045,10 +1019,7 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1408,19 +1379,19 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
     </row>
     <row r="3" spans="1:11" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -1430,7 +1401,7 @@
         <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>14</v>
@@ -1451,7 +1422,7 @@
         <v>19</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="K3" s="2"/>
     </row>
@@ -1461,7 +1432,7 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>20</v>
@@ -1487,19 +1458,19 @@
       <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
     </row>
     <row r="6" spans="1:11" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -1509,7 +1480,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>28</v>
@@ -1540,7 +1511,7 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>34</v>
@@ -1563,9 +1534,7 @@
       <c r="J7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>39</v>
-      </c>
+      <c r="K7" s="2"/>
     </row>
     <row r="8" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
@@ -1573,7 +1542,7 @@
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>34</v>
@@ -1582,23 +1551,21 @@
         <v>15</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="K8" s="2"/>
     </row>
     <row r="9" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
@@ -1606,7 +1573,7 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>34</v>
@@ -1615,23 +1582,21 @@
         <v>15</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>49</v>
-      </c>
+      <c r="K9" s="2"/>
     </row>
     <row r="10" spans="1:11" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -1639,55 +1604,55 @@
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
     </row>
     <row r="12" spans="1:11" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>28</v>
@@ -1696,29 +1661,29 @@
         <v>15</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="K12" s="2"/>
     </row>
     <row r="13" spans="1:11" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>28</v>
@@ -1727,29 +1692,29 @@
         <v>15</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="J13" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="K13" s="2"/>
     </row>
     <row r="14" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>28</v>
@@ -1758,139 +1723,139 @@
         <v>15</v>
       </c>
       <c r="F14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="J14" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="K14" s="2"/>
     </row>
     <row r="15" spans="1:11" ht="151.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="K15" s="2"/>
     </row>
     <row r="16" spans="1:11" ht="151.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="K16" s="2"/>
     </row>
     <row r="17" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
+      <c r="A17" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
     </row>
     <row r="18" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K18" s="2"/>
     </row>
     <row r="19" spans="1:11" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>28</v>
@@ -1899,79 +1864,77 @@
         <v>15</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="K19" s="6" t="s">
-        <v>86</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="K19" s="2"/>
     </row>
     <row r="20" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E20" s="7" t="s">
-        <v>87</v>
+      <c r="E20" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>19</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="K20" s="2"/>
     </row>
     <row r="21" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
+      <c r="A21" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
     </row>
     <row r="22" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>34</v>
@@ -1980,60 +1943,60 @@
         <v>15</v>
       </c>
       <c r="F22" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J22" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>97</v>
       </c>
       <c r="K22" s="2"/>
     </row>
     <row r="23" spans="1:11" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F23" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J23" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="K23" s="2"/>
     </row>
     <row r="24" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>28</v>
@@ -2042,31 +2005,31 @@
         <v>15</v>
       </c>
       <c r="F24" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="J24" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="K24" s="2"/>
     </row>
     <row r="25" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>34</v>
@@ -2075,29 +2038,29 @@
         <v>15</v>
       </c>
       <c r="F25" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J25" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="K25" s="2"/>
     </row>
     <row r="26" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>28</v>
@@ -2106,46 +2069,46 @@
         <v>15</v>
       </c>
       <c r="F26" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J26" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="K26" s="2"/>
+    </row>
+    <row r="27" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="H26" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="K26" s="2"/>
-    </row>
-    <row r="27" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
     </row>
     <row r="28" spans="1:11" ht="55.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>28</v>
@@ -2154,29 +2117,29 @@
         <v>15</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="K28" s="2"/>
     </row>
     <row r="29" spans="1:11" ht="78" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>28</v>
@@ -2185,60 +2148,60 @@
         <v>15</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="K29" s="2"/>
     </row>
     <row r="30" spans="1:11" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="K30" s="2"/>
     </row>
     <row r="31" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>34</v>
@@ -2247,139 +2210,139 @@
         <v>15</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="K31" s="2"/>
     </row>
     <row r="32" spans="1:11" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>19</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="K32" s="2"/>
     </row>
     <row r="33" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9"/>
+      <c r="A33" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
     </row>
     <row r="34" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="K34" s="2"/>
     </row>
     <row r="35" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="K35" s="2"/>
     </row>
     <row r="36" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>34</v>
@@ -2388,77 +2351,77 @@
         <v>15</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="K36" s="2"/>
     </row>
     <row r="37" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K37" s="2"/>
     </row>
     <row r="38" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
+      <c r="A38" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
     </row>
     <row r="39" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>28</v>
@@ -2467,112 +2430,112 @@
         <v>15</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="K39" s="2"/>
     </row>
     <row r="40" spans="1:11" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="K40" s="2"/>
     </row>
     <row r="41" spans="1:11" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K41" s="2"/>
     </row>
     <row r="42" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
-      <c r="J42" s="9"/>
-      <c r="K42" s="9"/>
+      <c r="A42" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
     </row>
     <row r="43" spans="1:11" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>28</v>
@@ -2581,46 +2544,46 @@
         <v>15</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="K43" s="2"/>
     </row>
     <row r="44" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
-      <c r="J44" s="9"/>
-      <c r="K44" s="9"/>
+      <c r="A44" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
     </row>
     <row r="45" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>28</v>
@@ -2629,60 +2592,60 @@
         <v>15</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="K45" s="2"/>
     </row>
     <row r="46" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="K46" s="2"/>
     </row>
     <row r="47" spans="1:11" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>28</v>
@@ -2691,258 +2654,256 @@
         <v>15</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="K47" s="2"/>
     </row>
     <row r="48" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E48" s="7" t="s">
-        <v>87</v>
+      <c r="E48" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="F48" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="K48" s="2"/>
+    </row>
+    <row r="49" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="G48" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="J48" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="K48" s="2"/>
-    </row>
-    <row r="49" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="9"/>
-      <c r="I49" s="9"/>
-      <c r="J49" s="9"/>
-      <c r="K49" s="9"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="8"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="8"/>
+      <c r="I49" s="8"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
     </row>
     <row r="50" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E50" s="7" t="s">
-        <v>87</v>
+      <c r="E50" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>273</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="K50" s="2"/>
     </row>
     <row r="51" spans="1:11" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E51" s="7" t="s">
-        <v>87</v>
+      <c r="E51" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>19</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="K51" s="2"/>
     </row>
     <row r="52" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="9"/>
-      <c r="I52" s="9"/>
-      <c r="J52" s="9"/>
-      <c r="K52" s="9"/>
+      <c r="A52" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
     </row>
     <row r="53" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>19</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="K53" s="2"/>
     </row>
     <row r="54" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="G54" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H54" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>215</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>19</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="K54" s="2"/>
     </row>
     <row r="55" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="9"/>
-      <c r="J55" s="9"/>
-      <c r="K55" s="9"/>
+      <c r="A55" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="B55" s="8"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="8"/>
+      <c r="I55" s="8"/>
+      <c r="J55" s="8"/>
+      <c r="K55" s="8"/>
     </row>
     <row r="56" spans="1:11" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>19</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="K56" s="2"/>
     </row>
@@ -2962,7 +2923,7 @@
     <mergeCell ref="A27:K27"/>
     <mergeCell ref="A21:K21"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>